--- a/docs/data/jp/xlsx/6923.xlsx
+++ b/docs/data/jp/xlsx/6923.xlsx
@@ -7680,7 +7680,7 @@
     <row r="101">
       <c r="A101" s="18" t="inlineStr">
         <is>
-          <t>Royalty Income NOI</t>
+          <t>로열티 수입</t>
         </is>
       </c>
       <c r="T101" s="20" t="n">
@@ -8174,7 +8174,7 @@
     <row r="112">
       <c r="A112" s="18" t="inlineStr">
         <is>
-          <t>Foreign Withholding Tax NOE</t>
+          <t>외국 원천세</t>
         </is>
       </c>
       <c r="C112" s="20" t="n">
@@ -8196,7 +8196,7 @@
     <row r="113">
       <c r="A113" s="18" t="inlineStr">
         <is>
-          <t>Compensation Expenses NOE</t>
+          <t>보상비 지급</t>
         </is>
       </c>
       <c r="H113" s="20" t="n">
@@ -8827,7 +8827,7 @@
     <row r="126">
       <c r="A126" s="18" t="inlineStr">
         <is>
-          <t>Business Structure Improvement Expenses EL</t>
+          <t>사업구조개선비용</t>
         </is>
       </c>
       <c r="F126" s="20" t="n">
@@ -8919,7 +8919,7 @@
     <row r="128">
       <c r="A128" s="18" t="inlineStr">
         <is>
-          <t>Loss On Abandonment Of Inventories EL</t>
+          <t>재고자산 폐기손실</t>
         </is>
       </c>
       <c r="C128" s="20" t="n">
@@ -8990,7 +8990,7 @@
     <row r="130">
       <c r="A130" s="18" t="inlineStr">
         <is>
-          <t>Special Survey Costs EL</t>
+          <t>특별조사비용</t>
         </is>
       </c>
       <c r="C130" s="20" t="n">
@@ -12250,7 +12250,7 @@
     <row r="198">
       <c r="A198" s="18" t="inlineStr">
         <is>
-          <t>Early Extra Retirement Payments Ope CF</t>
+          <t>조기 특별퇴직금</t>
         </is>
       </c>
       <c r="R198" s="20" t="n">
@@ -12707,7 +12707,7 @@
     <row r="208">
       <c r="A208" s="18" t="inlineStr">
         <is>
-          <t>Payments For Loss On Litigation Ope CF</t>
+          <t>소송 관련 손실 지급액</t>
         </is>
       </c>
       <c r="P208" s="20" t="n">
@@ -12723,7 +12723,7 @@
     <row r="209">
       <c r="A209" s="18" t="inlineStr">
         <is>
-          <t>Payment For Early Extra Retirement Payments Ope CF</t>
+          <t>조기 특별퇴직금 지급액</t>
         </is>
       </c>
       <c r="R209" s="20" t="n">
@@ -12797,7 +12797,7 @@
     <row r="211">
       <c r="A211" s="18" t="inlineStr">
         <is>
-          <t>Payments For Extra Retirement Payments Ope CF</t>
+          <t>특별퇴직금 지급액</t>
         </is>
       </c>
       <c r="C211" s="20" t="n">
@@ -12831,7 +12831,7 @@
     <row r="212">
       <c r="A212" s="18" t="inlineStr">
         <is>
-          <t>Payment For Loss From Money Transfer Scam At Foreign Subsidiary Ope CF</t>
+          <t>해외 자회사 송금사기 손실 지급액</t>
         </is>
       </c>
       <c r="E212" s="20" t="n">
@@ -13018,7 +13018,7 @@
     <row r="216">
       <c r="A216" s="18" t="inlineStr">
         <is>
-          <t>Payments Into Increase In Long Term Deposits Inv CF</t>
+          <t>장기 정기예금 예입 지출</t>
         </is>
       </c>
       <c r="C216" s="20" t="n">
@@ -13239,7 +13239,7 @@
     <row r="221">
       <c r="A221" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Sales Of Intangible Assets Inv CF</t>
+          <t>무형자산 매각 수입</t>
         </is>
       </c>
       <c r="E221" s="20" t="n">
@@ -13304,7 +13304,7 @@
     <row r="223">
       <c r="A223" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Sales And Redemption Of Short Term And Long Term Investment Securities Inv CF</t>
+          <t>유가증권·투자유가증권 매각·상환 수입</t>
         </is>
       </c>
       <c r="C223" s="20" t="n">
@@ -13755,7 +13755,7 @@
     <row r="233">
       <c r="A233" s="18" t="inlineStr">
         <is>
-          <t>Decrease Increase In Money Held In Trust For Purchase Of Treasury Stock Fin CF</t>
+          <t>자사주 취득용 금전신탁 증감액</t>
         </is>
       </c>
       <c r="C233" s="20" t="n">
@@ -13817,7 +13817,7 @@
     <row r="235">
       <c r="A235" s="18" t="inlineStr">
         <is>
-          <t>Payment Into Money Trust To Acquire Treasury Stock Fin CF</t>
+          <t>자사주 취득용 금전신탁 지출</t>
         </is>
       </c>
       <c r="T235" s="20" t="n">
@@ -18043,7 +18043,7 @@
     <row r="107">
       <c r="A107" s="18" t="inlineStr">
         <is>
-          <t>Investments In Capital Of Subsidiaries And Affiliates</t>
+          <t>관계회사 출자금</t>
         </is>
       </c>
       <c r="F107" s="20" t="n">
@@ -18093,7 +18093,7 @@
     <row r="109">
       <c r="A109" s="18" t="inlineStr">
         <is>
-          <t>Prepaid Pension Cost IOA</t>
+          <t>선급연금비용</t>
         </is>
       </c>
       <c r="F109" s="20" t="n">
@@ -18409,7 +18409,7 @@
     <row r="119">
       <c r="A119" s="18" t="inlineStr">
         <is>
-          <t>Current Portion Of Bonds</t>
+          <t>1년 내 상환 예정 사채</t>
         </is>
       </c>
       <c r="I119" s="20" t="n">
@@ -18713,7 +18713,7 @@
     <row r="129">
       <c r="A129" s="18" t="inlineStr">
         <is>
-          <t>Special Retirement Allowance CL</t>
+          <t>특별퇴직충당금</t>
         </is>
       </c>
       <c r="J129" s="20" t="n">
@@ -18918,7 +18918,7 @@
     <row r="136">
       <c r="A136" s="18" t="inlineStr">
         <is>
-          <t>Long Term Income Taxes Payable</t>
+          <t>장기 미지급 법인세</t>
         </is>
       </c>
       <c r="F136" s="20" t="n">
